--- a/week6/homework-clustering-pca-rnn.xlsx
+++ b/week6/homework-clustering-pca-rnn.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="119">
   <si>
     <t xml:space="preserve">[Description] K-Means, Hierarchical Clustering, PVE &amp; a Tiny RNN</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t xml:space="preserve">average of cluster-1 points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Answer:</t>
   </si>
   <si>
     <t xml:space="preserve">New centroid c₁: y =</t>
@@ -1002,7 +1005,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1171,99 +1174,111 @@
       <c r="A19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="D19" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF(F19="","",IF(ROUND(F19,3)=ROUND(1,3),"✓","✗"))</f>
+      <c r="F19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF(G19="","",IF(ROUND(G19,3)=ROUND(1,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="11"/>
+        <v>46</v>
+      </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="5" t="str">
-        <f aca="false">IF(F21="","",IF(ROUND(F21,3)=ROUND(1.5,3),"✓","✗"))</f>
+      <c r="F21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="5" t="str">
+        <f aca="false">IF(G21="","",IF(ROUND(G21,3)=ROUND(1.5,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="5" t="str">
-        <f aca="false">IF(F23="","",IF(ROUND(F23,3)=ROUND(4.5,3),"✓","✗"))</f>
+      <c r="F23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="5" t="str">
+        <f aca="false">IF(G23="","",IF(ROUND(G23,3)=ROUND(4.5,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="11"/>
+        <v>49</v>
+      </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="5" t="str">
-        <f aca="false">IF(F25="","",IF(ROUND(F25,3)=ROUND(3.75,3),"✓","✗"))</f>
+      <c r="F25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="5" t="str">
+        <f aca="false">IF(G25="","",IF(ROUND(G25,3)=ROUND(3.75,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="11"/>
+      <c r="D29" s="11" t="s">
+        <v>52</v>
+      </c>
       <c r="E29" s="11"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="5" t="str">
-        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))=UPPER("p2"),"✓","✗"))</f>
+      <c r="F29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="5" t="str">
+        <f aca="false">IF(G29="","",IF(UPPER(TRIM(G29))=UPPER("p2"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="11"/>
+        <v>53</v>
+      </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="5" t="str">
-        <f aca="false">IF(F31="","",IF(ROUND(F31,3)=ROUND(3,3),"✓","✗"))</f>
+      <c r="F31" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="12"/>
+      <c r="H31" s="5" t="str">
+        <f aca="false">IF(G31="","",IF(ROUND(G31,3)=ROUND(3,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D31:E31"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J31">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1288,7 +1303,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="8"/>
@@ -1296,42 +1311,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0</v>
@@ -1348,7 +1363,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>1</v>
@@ -1365,7 +1380,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>4</v>
@@ -1382,7 +1397,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>5.1</v>
@@ -1399,94 +1414,106 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="5" t="str">
-        <f aca="false">IF(F15="","",IF(UPPER(TRIM(F15))=UPPER("A-B"),"✓","✗"))</f>
+      <c r="F15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="5" t="str">
+        <f aca="false">IF(G15="","",IF(UPPER(TRIM(G15))=UPPER("A-B"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="11"/>
+        <v>64</v>
+      </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="5" t="str">
-        <f aca="false">IF(F17="","",IF(ROUND(F17,3)=ROUND(1,3),"✓","✗"))</f>
+      <c r="F17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="5" t="str">
+        <f aca="false">IF(G17="","",IF(ROUND(G17,3)=ROUND(1,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="11"/>
+        <v>65</v>
+      </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))=UPPER("C-D"),"✓","✗"))</f>
+      <c r="F19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF(G19="","",IF(UPPER(TRIM(G19))=UPPER("C-D"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="11"/>
+        <v>66</v>
+      </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="5" t="str">
-        <f aca="false">IF(F21="","",IF(ROUND(F21,3)=ROUND(1.41,3),"✓","✗"))</f>
+      <c r="F21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="5" t="str">
+        <f aca="false">IF(G21="","",IF(ROUND(G21,3)=ROUND(1.41,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11" t="s">
+        <v>68</v>
+      </c>
       <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="5" t="str">
-        <f aca="false">IF(F23="","",IF(ROUND(F23,3)=ROUND(5.1,3),"✓","✗"))</f>
+      <c r="F23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="5" t="str">
+        <f aca="false">IF(G23="","",IF(ROUND(G23,3)=ROUND(5.1,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="11"/>
+        <v>69</v>
+      </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="5" t="str">
-        <f aca="false">IF(F25="","",IF(ROUND(F25,3)=ROUND(2,3),"✓","✗"))</f>
+      <c r="F25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="5" t="str">
+        <f aca="false">IF(G25="","",IF(ROUND(G25,3)=ROUND(2,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D25:E25"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J25">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1511,7 +1538,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1523,41 +1550,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>36</v>
@@ -1621,38 +1648,42 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="5" t="str">
-        <f aca="false">IF(F17="","",IF(ROUND(F17,3)=ROUND(10,3),"✓","✗"))</f>
+      <c r="F17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="5" t="str">
+        <f aca="false">IF(G17="","",IF(ROUND(G17,3)=ROUND(10,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="11" t="s">
+        <v>81</v>
+      </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF(F19="","",IF(ROUND(F19,3)=ROUND(2,3),"✓","✗"))</f>
+      <c r="F19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF(G19="","",IF(ROUND(G19,3)=ROUND(2,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D19:E19"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J19">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1677,7 +1708,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="6"/>
@@ -1688,41 +1719,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>36</v>
@@ -1772,36 +1803,40 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="11"/>
+        <v>91</v>
+      </c>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="5" t="str">
-        <f aca="false">IF(F16="","",IF(ROUND(F16,3)=ROUND(3,3),"✓","✗"))</f>
+      <c r="F16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="5" t="str">
+        <f aca="false">IF(G16="","",IF(ROUND(G16,3)=ROUND(3,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="5" t="str">
-        <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))=UPPER("Yes"),"✓","✗"))</f>
+      <c r="F18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="5" t="str">
+        <f aca="false">IF(G18="","",IF(UPPER(TRIM(G18))=UPPER("Yes"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J18">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1835,38 +1870,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>38</v>
@@ -1874,28 +1909,28 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>2</v>
@@ -1903,7 +1938,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1911,20 +1946,20 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>2</v>
@@ -1932,28 +1967,28 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>3</v>

--- a/week6/homework-clustering-pca-rnn.xlsx
+++ b/week6/homework-clustering-pca-rnn.xlsx
@@ -391,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,6 +464,26 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -487,7 +507,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD8E4BC"/>
-        <bgColor rgb="FFDAEEF3"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -636,15 +656,15 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFAA433F"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFDAEEF3"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF1E64C8"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -668,7 +688,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFCC8F8E"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -680,6 +700,720 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="12"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Your scree plot</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Step3_PVE!C11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="AA433F"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="AA433F"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="AA433F"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="12600">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Step3_PVE!$A$12:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Step3_PVE!$C$12:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Step3_PVE!D11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cumulative PVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="CC8F8E"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="CC8F8E"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="CC8F8E"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="12600">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Step3_PVE!$A$12:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Step3_PVE!$D$12:$D$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="18131043"/>
+        <c:axId val="63785986"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="18131043"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Principal component</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="63785986"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="63785986"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Proportion of variance explained</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="18131043"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>399240</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4276800" y="1905120"/>
+        <a:ext cx="4679640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1700,6 +2434,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
